--- a/excel/KIDS report templates.xlsx
+++ b/excel/KIDS report templates.xlsx
@@ -4,16 +4,16 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="XPLORER" sheetId="1" r:id="rId1"/>
-    <sheet name="GAMEDEV" sheetId="2" r:id="rId2"/>
-    <sheet name="WEBDEV" sheetId="3" r:id="rId3"/>
-    <sheet name="PYTHON_CODER" sheetId="4" r:id="rId4"/>
-    <sheet name="PYTHON_GAMER" sheetId="5" r:id="rId5"/>
-    <sheet name="PYTHON_AI" sheetId="6" r:id="rId6"/>
-    <sheet name="ROBLOX_EXPLORER" sheetId="7" r:id="rId7"/>
-    <sheet name="ROBLOX_DESIGNER" sheetId="8" r:id="rId8"/>
-    <sheet name="ROBLOX_CODER" sheetId="9" r:id="rId9"/>
-    <sheet name="ROBLOX_ADVANCE CODER" sheetId="10" r:id="rId10"/>
-    <sheet name="TECH_EXPLORER" sheetId="11" r:id="rId11"/>
+    <sheet name="WEBDEV" sheetId="2" r:id="rId2"/>
+    <sheet name="PYTHON_CODER" sheetId="3" r:id="rId3"/>
+    <sheet name="PYTHON_GAMER" sheetId="4" r:id="rId4"/>
+    <sheet name="PYTHON_AI" sheetId="5" r:id="rId5"/>
+    <sheet name="TECH_EXPLORER" sheetId="6" r:id="rId6"/>
+    <sheet name="GAMEDEV" sheetId="7" r:id="rId7"/>
+    <sheet name="ROBLOX_EXPLORER" sheetId="8" r:id="rId8"/>
+    <sheet name="ROBLOX_DESIGNER" sheetId="9" r:id="rId9"/>
+    <sheet name="ROBLOX_CODER" sheetId="10" r:id="rId10"/>
+    <sheet name="ROBLOX_ADVANCE CODER" sheetId="11" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
@@ -708,7 +708,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Khadijah has shown impressive progress this term. She was able to implement intermediate programming concepts in various exercises and projects such as list, broadcast and clone. Khadijah also understand how to create more complex programs and get introduced to Python. Great job!</v>
+        <v>[NAMA_STUDENT] menunjukkan progress yang [sangat mengesankan/ mengesankan/ cukup baik] pada level ini. [NAMA_STUDENT] mampu menerapkan konsep pemrograman tingkat menengah dalam berbagai latihan dan proyek, seperti list, broadcast, dan clone. [NAMA_STUDENT] juga memahami cara membuat program yang lebih kompleks dan mulai dikenalkan dengan Python. Good job [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="50">
@@ -892,223 +892,281 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:A54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>*for report  in english, just translate this</v>
+        <v>ROBLOX CODER 1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>*for character, make it different for each students</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Nilai</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Konversi Kualitas</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Encouragement (ENG)</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Character</v>
+        <v>Coding Literacy and Concept</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ROBLOX ADVANCE CODER 1</v>
-      </c>
-      <c r="G3" t="str">
-        <v>I can tell you’re working hard—stay with it!</v>
-      </c>
-      <c r="H3" t="str">
-        <v>aktif</v>
+        <v>NOTES</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Coding Literacy and Concept</v>
-      </c>
-      <c r="E4" t="str">
-        <v>A</v>
-      </c>
-      <c r="F4" t="str">
-        <v>sangat baik</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Encouragement (IND)</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>NOTES</v>
-      </c>
-      <c r="E5" t="str">
-        <v>B</v>
-      </c>
-      <c r="F5" t="str">
-        <v>baik</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Mantap, Lajutkan ya!</v>
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] dasar-dasar coding di Roblox Studio, yaitu variable, properti, reusing code, function, dan conditional statement. [NAMA_STUDENT] juga memahami konsep leaderboard dan cara kerja sell platform pada game. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Well done [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B6" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C6" t="str">
-        <v>VARIASI 3</v>
-      </c>
-      <c r="E6" t="str">
-        <v>C</v>
-      </c>
-      <c r="F6" t="str">
-        <v>cukup baik</v>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Coding Practice</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa mengerjakan latihan coding dengan [sangat baik/ baik/ cukup baik]. [NAMA_STUDENT] berhasil membuat obby game, menerapkan terrain editor untuk membuat adventure game, menambahkan tool effect dan leaderboard, serta membuat harvestable item dan sell platform menggunakan conditional statement. Good job [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B11" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C11" t="str">
-        <v>VARIASI 3</v>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ROBLOX ADVANCE CODER 2</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Coding Literacy and Concept</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>NOTES</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B19" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C19" t="str">
-        <v>VARIASI 3</v>
+        <v>ROBLOX CODER 2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Coding Literacy and Concept</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Coding Practice</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep coding lanjutan di Roblox Studio, yaitu event, module script, remote event, click detector, dan cara membuat animasi. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Awesome [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B24" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C24" t="str">
-        <v>VARIASI 3</v>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>[NAMA_STUDENT] bisa menerapkan konsep coding dengan [sangat baik/ baik/ cukup baik]. [NAMA_STUDENT] berhasil membuat custom player character yang bisa digerakkan dan menembak, membuat screen gui yang dinamis dengan remote event, menerapkan animasi ke dalam story game, serta menggunakan click detector untuk menjalankan task dalam game. Nice work [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ROBLOX ADVANCE CODER 3</v>
+        <v>Character</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Coding Literacy and Concept</v>
+        <v>NOTES</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>NOTES</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B33" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C33" t="str">
-        <v>VARIASI 3</v>
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Coding Practice</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>NOTES</v>
+        <v>ROBLOX CODER 3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B38" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C38" t="str">
-        <v>VARIASI 3</v>
+        <v>Coding Literacy and Concept</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] proses pengembangan game secara menyeluruh, mulai dari perencanaan, penulisan kode utama, debugging, hingga memahami sistem monetisasi Robux di Roblox. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Great job [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>[NAMA_STUDENT] bisa menerapkan seluruh konsep yang sudah dipelajari dengan [sangat baik/ baik/ cukup baik] untuk membuat game sendiri. [NAMA_STUDENT] merancang dan membangun model serta lingkungan game, menulis dan menyempurnakan kode utama, memperbaiki bug, menunjukkan progress dan menerima feedback dari teman sekelas, hingga mempresentasikan game yang sudah selesai. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A54"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1119,7 +1177,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>TECH EXPLORER 1</v>
+        <v>ROBLOX ADVANCE CODER 1</v>
       </c>
     </row>
     <row r="2">
@@ -1139,7 +1197,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>[NAMA_STUDENT] bisa memahami konsep coding dasar dengan [sangat baik/ baik/ cukup baik], yaitu algoritma, event, dan loop. [NAMA_STUDENT] juga mempelajari literasi digital seperti kecanduan game (game loop, login harian, FOMO saat event game online), probabilitas (RNG) dalam permainan, strategi top up game yang bijak, dan bahaya bubble information. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Well done [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep game development battle royale, yaitu multiplayer game loop, table dan for loop in pairs, teleport system, serta timer module. [NAMA_STUDENT] juga memahami alur sistem match, mulai dari player kalah, mengakhiri match, hingga reset state untuk babak berikutnya. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Well done [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="6">
@@ -1164,7 +1222,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>[NAMA_STUDENT] bisa mengerjakan latihan coding dan desain dengan [sangat baik/ baik/ cukup baik]. Latihan tersebut meliputi membuat project Virtual Reality (VR) yang lebih canggih dan project Augmented Reality (AR) di DelightEx — seperti mendesain Merge Cube, membuat kuis interaktif, mengunggah video, mendesain rumah sederhana dengan konsep warna 3D, serta menambahkan animasi dan teks. Good job [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] bisa menerapkan konsep coding dengan [sangat baik/ baik/ cukup baik]. [NAMA_STUDENT] berhasil membuat lobby system dengan teleport system, coding sword, health potion, dan gun player, membuat screen gui yang dinamis dengan timer module, serta menerapkan sistem kembali ke lobby dan intermission setelah match selesai. Good job [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="11">
@@ -1209,7 +1267,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>TECH EXPLORER 2</v>
+        <v>ROBLOX ADVANCE CODER 2</v>
       </c>
     </row>
     <row r="20">
@@ -1229,7 +1287,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep-konsep coding block pada Scratch, yaitu event, loop, broadcast, looping control (perulangan), dan conditional logic (percabangan). [NAMA_STUDENT] juga mempelajari literasi digital seperti bahaya stranger danger di dunia maya, keamanan digital melalui QR Code, manfaat dan keamanan cloud storage, serta cara kerja search engine. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Awesome [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep placement system dan cara kerja game Cleaner Boat Simulator, termasuk sistem collecting trash dan proses upgrade boat menggunakan quiz. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Awesome [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="24">
@@ -1254,7 +1312,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>[NAMA_STUDENT] bisa mengoperasikan Scratch dan menerapkan block coding dengan [sangat baik/ baik/ cukup baik], mulai dari block Motion, Looks, Sound, hingga Sensing. [NAMA_STUDENT] berhasil membuat beberapa project seperti animasi sederhana, Beetle Race Game, dan Bug Hunter Game menggunakan konsep conditional. Nice work [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] bisa menerapkan konsep coding dengan [sangat baik/ baik/ cukup baik]. [NAMA_STUDENT] berhasil membuat screen GUI untuk memilih dan menyusun bagian boat, coding untuk launch boat dan collecting trash, menampilkan jumlah sampah di screen gui, serta membuat quiz gui untuk sistem upgrade boat. Nice work [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="29">
@@ -1299,7 +1357,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>TECH EXPLORER 3</v>
+        <v>ROBLOX ADVANCE CODER 3</v>
       </c>
     </row>
     <row r="38">
@@ -1319,7 +1377,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep coding lanjutan pada Scratch, yaitu operator, variable, list, dan function (My Blocks), serta konsep otomasi dalam kehidupan sehari-hari. [NAMA_STUDENT] juga mempelajari literasi digital seperti membuat password yang kuat, mengenali deepfake, dasar teknologi Generative AI, teknik prompting yang efektif, dan etika/kejujuran dalam berkarya dengan AI. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Great job [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep game Math Obby, yaitu menampilkan soal matematika secara dinamis melalui screen GUI dan memeriksa jawaban player, serta memahami fitur Game Pass di Roblox. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Great job [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="42">
@@ -1344,7 +1402,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>[NAMA_STUDENT] bisa menerapkan seluruh konsep yang sudah dipelajari dengan [sangat baik/ baik/ cukup baik] untuk menyelesaikan project game final. [NAMA_STUDENT] mengumpulkan asset game (termasuk dari AI), mengintegrasikan AI Buddy ke dalam VR Edu Delightex, menyelesaikan tahap coding project, hingga mempresentasikan hasil project dengan baik. Keep it up [NAMA_STUDENT] !</v>
+        <v>[NAMA_STUDENT] bisa menerapkan seluruh konsep yang sudah dipelajari dengan [sangat baik/ baik/ cukup baik] untuk membuat game sendiri. [NAMA_STUDENT] merancang lingkungan dan model game, menulis kode utama (logika, variabel, dan fungsi penting), melakukan testing dan debugging, menambahkan fitur Game Pass, hingga mempresentasikan game yang telah selesai kepada teman-teman sekelas. Keep it up [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="47">
@@ -1395,277 +1453,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H46"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>*for report  in english, just translate this</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>*for character, make it different for each students</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Nilai</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Konversi Kualitas</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Encouragement (ENG)</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Character</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>GAME DEV 1</v>
-      </c>
-      <c r="G3" t="str">
-        <v>I can tell you’re working hard—stay with it!</v>
-      </c>
-      <c r="H3" t="str">
-        <v>aktif</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Coding Literacy and Concept</v>
-      </c>
-      <c r="E4" t="str">
-        <v>A</v>
-      </c>
-      <c r="F4" t="str">
-        <v>sangat baik</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Encouragement (IND)</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>NOTES</v>
-      </c>
-      <c r="E5" t="str">
-        <v>B</v>
-      </c>
-      <c r="F5" t="str">
-        <v>baik</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Mantap, Lajutkan ya!</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B6" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C6" t="str">
-        <v>VARIASI 3</v>
-      </c>
-      <c r="E6" t="str">
-        <v>C</v>
-      </c>
-      <c r="F6" t="str">
-        <v>cukup baik</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v xml:space="preserve"> Pada level Game Development 1, [NAMA_STUDENT] mempelajari penggunaan framework construct3 untuk membuat 2D game. [NAMA_STUDENT]  menggunakannya dengan [sangat baik/ baik/ cukup baik]. Konsep layout, object, behavior, variable dan event sheet termasuk event dan sub-event juga dipahami dengan cukup baik. Nilai ujian konsep [NAMA_STUDENT]  adalah [MASUKAN_NILAI UJIAN]. Keep it up ya [NAMA_STUDENT] !</v>
-      </c>
-      <c r="B7" t="str">
-        <v>In Game Development 1, Zayyan has been learning the Construct 3 framework for 2D game creation. Zayyan has utilized it well. The concepts of layouts, objects, behaviors, variables, and event sheets, including events and sub-events, are also understood well enough. Zayyan's concept exam score is 100 out of 100. Keep it up, Zayyan!</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Coding Practice</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>NOTES</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B11" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C11" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>[NAMA_STUDENT]  bisa menambahkan object sprite, background, text, dan behavior seperti Jump-thru, solid, platform, rotate, sine, bullet dan 8Direction. Pada level ini, ada 4 project game. [NAMA_STUDENT]  mengerjakannya dengan [sangat baik/ baik/ cukup baik]. Namun, Saat ujian coding, yaitu membuat sebuah game,  [NAMA_STUDENT]  tidak menyelesaikannya dengan baik. Kedepannya lebih baik lagi dan tingkatkan semangatnya ya [NAMA_STUDENT]!</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Zayyan is able to add sprite objects, backgrounds, text, and behaviors such as Jump-thru, solid, platform, rotate, sine, bullet, and 8Direction. In this level, there were 4 game projects. Zayyan completed them very well. Furthermore, during the coding exam, Zayyan also finish creating the game. Moving forward, keep that enthusiasm high, Zayyan!</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>GAME DEV 2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Coding Literacy and Concept</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>NOTES</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B19" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C19" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="20" xml:space="preserve">
-      <c r="A20" t="str" xml:space="preserve">
-        <v xml:space="preserve">
-Progress [NAMA_STUDENT][sangat signifikan/ signifikan/ cukup signifikan] menggunakan framework construct3 dalam membuat game. Konsep layout game, seperti start, game, gameover dan win layout bisa dipahami [NAMA_STUDENT] dengan [cukup baik/ baik/ sangat baik]. Konsep obstacles, enemies, family features, particles, aim and shoot, change costume and impulse juga bisa dipahami dengan baik. [NAMA_STUDENT] mendapatkan nilai ujian [MASUKAN_NILAI UJIAN]. Pertahankan semangatnya ya [NAMA_STUDENT]!</v>
-      </c>
-      <c r="B20" t="str">
-        <v>In Game Development 2, Khadijah continued to develop her understanding of Construct 3 by learning more advanced concepts such as instance variables, random mechanics, player selection, life and score systems, and Game Over logic. Compared to Level 1, she showed a stronger grasp of how these systems connect together in a full game. On her written concept exam, Khadijah scored 80 out of 100, which reflects a good understanding of the material. Well done, Khadijah!</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Coding Practice</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>NOTES</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B24" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C24" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="25" xml:space="preserve">
-      <c r="A25" t="str" xml:space="preserve">
-        <v xml:space="preserve">[NAMA_STUDENT] membuat dua game pada level ini. Game yang dibuat semakin kompleks, menggunakan intermediate konsep. [NAMA_STUDENT] berhasil menyelesaikannya dengan [sangat baik/ baik/ cukup baik]. Namun, saat ujian coding, membuat game juga, [NAMA_STUDENT] [cukup/sedikit kesulitan/ tidak ada kesulitan] untuk menyelesaikannya. James menyelesaikannya dalam [JUMLAH PERTEMUAN] pertemuan. Kedepannya lebih banyak latihan codingnya dan tingkatkan semangatnya ya[NAMA_STUDENT] !
-</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Khadijah built a more complex and complete game this level, applying advanced features like bouncing ball mechanics, floating blocks, layout and button design, life counter, score tracker, family feature, and instance variables — going beyond what she created in Level 1. For her coding exam, she successfully completed the project and met all the required criteria. Notably, when her project file was lost mid-course, she redid the entire game from scratch and completed it well. Keep up the good work, Khadijah!</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>GAME DEV 3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Coding Literacy and Concept</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>NOTES</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B32" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C32" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="33" xml:space="preserve">
-      <c r="A33" t="str" xml:space="preserve">
-        <v xml:space="preserve">[NAMA_STUDENT] semakin mahir menggunakan menggunakan framework construct3. [NAMA_STUDENT] bisa membuat layout dengan menggunakan konsep tilemap, konsep behaviour scroll to, anchor, dan jump-thru. Konsep-konsep yang dipelajari pada level ini cukup advance dan dapat dipahami dengan [sangat baik/ baik/ cukup baik]. [NAMA_STUDENT] juga bisa men-deploy game yang sudah dibuat ke website. Great Job [NAMA_STUDENT] !
-_x000d_
-</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Coding Practice</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>NOTES</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B37" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C37" t="str">
-        <v>VARIASI 3</v>
-      </c>
-    </row>
-    <row r="38" xml:space="preserve">
-      <c r="A38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pada level ini game yang dbuat hanya 1 tapi game ini lebih kompleks dari yang sebelumnya pernah dibuat.  [NAMA_STUDENT] berhasil menyelesaikannya dengan [sangat baik/ baik/ cukup baik].Untuk project akhir yaitu membuat game sendiri, dimulai dari ide, design, coding sampai presentasi dan demo game, [NAMA_STUDENT] mampu menyelesaikan dengan [sangat baik/ baik/ cukup baik]. Game yang dibuat menarik untuk dimainkan. Berikut link gamenya: [LINK_GAME]
-</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-  </mergeCells>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H46"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H62"/>
   <sheetData>
@@ -2027,7 +1814,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H38"/>
   <sheetData>
@@ -2194,7 +1981,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>El show good understanding of intermediate Python concepts in practice. He has learned OOP fundamentals, Python modules introduction, and TKinter GUI development. Key topics covered include OOP principles, module basics, TKinter components, message/input boxes, labels, buttons, canvas coordinates, and event handling concepts. While his theoretical exam needs improvement, his practical application shows strong conceptual grasp. Keep it up, El!</v>
+        <v>[NAMA_STUDENT] menunjukkan pemahaman yang [sangat baik/ baik/ cukup baik] terhadap konsep Python tingkat menengah. [NAMA_STUDENT] mempelajari dasar-dasar OOP, pengenalan module Python, dan pengembangan GUI dengan TKinter. Topik yang dipelajari meliputi prinsip OOP, dasar module, komponen TKinter, message/input box, label, button, canvas coordinates, dan konsep event handling. Keep it up, [NAMA_STUDENT] !</v>
       </c>
       <c r="B25" t="str">
         <v>Araya mempelajari topik-topik Python tingkat menengah di Level 2, mulai dari Object Oriented Programming (OOP), penggunaan modul Python, hingga membuat tampilan aplikasi desktop menggunakan TKinter—termasuk tombol, label, kotak input, canvas, dan interaksi mouse. Nilai ujian teorinya 70 dari 100, yang menunjukkan pemahamannya masih bisa terus diasah. Ke depannya, Araya bisa lebih sering mengulang konsep-konsep yang dipelajari agar semakin kuat pemahamannya. Tetap semangat, Araya!</v>
@@ -2226,7 +2013,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>El applies learned concepts with good consistency. The programming exercises were completed successfully, showing steady progress in GUI development. Challenge projects were approached with determination. He also successfully finished the exam. Next focus is on improving code understanding for the next level. You're on track, El!</v>
+        <v>[NAMA_STUDENT] bisa menerapkan konsep yang dipelajari dengan [sangat baik/ baik/ cukup baik] dan konsisten. Latihan pemrograman diselesaikan dengan baik, menunjukkan progress yang stabil dalam pengembangan GUI. Project challenge dikerjakan dengan penuh determinasi, dan [NAMA_STUDENT] juga berhasil menyelesaikan ujiannya. You're on track, [NAMA_STUDENT] !</v>
       </c>
       <c r="B30" t="str">
         <v>Araya berhasil menyelesaikan semua latihan dan challenge dengan cukup baik. Pada ujian coding project, ia berhasil menyelesaikan proyeknya meski masih perlu beberapa kali bertanya—yang merupakan hal yang wajar dan menunjukkan ia mau berusaha sampai selesai. Ke depannya, Araya bisa berlatih mengerjakan proyek secara lebih mandiri agar semakin percaya diri. Good job, Araya!</v>
@@ -2258,7 +2045,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>El is very active in class. He asks relevant questions about material when needed, showing interest in learning new programming concepts. El usually stays focused during lessons, though occasionally needs gentle reminders when topics become challenging, when he gets overly energetic, or on days when he's feeling tired. Keep it up, El!</v>
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di dalam kelas. [NAMA_STUDENT] mengajukan pertanyaan relevan tentang materi saat diperlukan, menunjukkan minat dalam mempelajari konsep pemrograman baru. [NAMA_STUDENT] biasanya tetap fokus selama pelajaran, meski kadang butuh pengingat halus saat materi menjadi menantang. Keep it up, [NAMA_STUDENT] !</v>
       </c>
       <c r="C35" t="str">
         <v>Araya sangat aktif di dalam kelas dan selalu menunjukkan antusiasme yang tinggi dalam mempelajari konsep pemrograman baru. Ia tidak ragu untuk mengajukan pertanyaan yang relevan. Araya umumnya mampu menjaga fokus, meskipun terkadang membutuhkan pengingat dari pengajar saat ia merasa terlalu bersemangat atau ketika materi mulai menjadi lebih menantang.</v>
@@ -2289,7 +2076,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H40"/>
   <sheetData>
@@ -2516,7 +2303,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H39"/>
   <sheetData>
@@ -2743,706 +2530,1127 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:A54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>*for report  in english, just translate this</v>
+        <v>TECH EXPLORER 1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>*for character, make it different for each students</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Nilai</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Konversi Kualitas</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Encouragement (ENG)</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Character</v>
+        <v>Coding Literacy and Concept</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ROBLOX EXPLORER 1</v>
-      </c>
-      <c r="G3" t="str">
-        <v>I can tell you’re working hard—stay with it!</v>
-      </c>
-      <c r="H3" t="str">
-        <v>aktif</v>
+        <v>NOTES</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Digital &amp; Studio Literacy</v>
-      </c>
-      <c r="E4" t="str">
-        <v>A</v>
-      </c>
-      <c r="F4" t="str">
-        <v>sangat baik</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Encouragement (IND)</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>NOTES</v>
-      </c>
-      <c r="E5" t="str">
-        <v>B</v>
-      </c>
-      <c r="F5" t="str">
-        <v>baik</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Mantap, Lajutkan ya!</v>
+        <v>[NAMA_STUDENT] bisa memahami konsep coding dasar dengan [sangat baik/ baik/ cukup baik], yaitu algoritma, event, dan loop. [NAMA_STUDENT] juga mempelajari literasi digital seperti kecanduan game (game loop, login harian, FOMO saat event game online), probabilitas (RNG) dalam permainan, strategi top up game yang bijak, dan bahaya bubble information. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Well done [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B6" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C6" t="str">
-        <v>VARIASI 3</v>
-      </c>
-      <c r="E6" t="str">
-        <v>C</v>
-      </c>
-      <c r="F6" t="str">
-        <v>cukup baik</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Eymar learned about computer parts, Roblox Studio basics, and digital literacy topics such as screen time, cyberbullying, and copyrights. He understands how to navigate the studio interface and use its tools to create and edit 3D objects. Eymar explored the Toolbox for assets, learned terrain creation, and successfully published his game to Roblox platform. He shows good understanding of both technical and digital citizenship concepts.</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Araya mempelajari tentang komponen komputer, fitur dasar di Roblox Studio, dan literasi digital, seperti screen time, cyberbullying, dan copyrights. Araya bisa memahami dengan sangat baik. Good Job Araya!</v>
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Design Concept &amp; Practice</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa mengerjakan latihan coding dan desain dengan [sangat baik/ baik/ cukup baik]. Latihan tersebut meliputi membuat project Virtual Reality (VR) yang lebih canggih dan project Augmented Reality (AR) di DelightEx — seperti mendesain Merge Cube, membuat kuis interaktif, mengunggah video, mendesain rumah sederhana dengan konsep warna 3D, serta menambahkan animasi dan teks. Good job [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B11" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C11" t="str">
-        <v>VARIASI 3</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Eymar developed foundational design skills in Roblox Studio, including part transformation, game appearance, basic modeling, and terrain editor. He created projects such as Simple House and Village in Small Island, practicing how to imitate real objects from images into 3D models. Eymar learned to use visual effects and combine elements to build environments. To improve further, he can focus on adding more details and refining designs.</v>
-      </c>
-      <c r="B12" t="str">
-        <v xml:space="preserve">Araya mengembangkan keterampilan desain dasar di Roblox Studio, seperti transformasi part, tampilan game, dasar modeling, dan terrain editor untuk membuat proyek, seperti Rumah dan Desa di Pulau Kecil. Araya juga belajar menggunakan toolbox dan effect. </v>
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Character</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B16" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C16" t="str">
-        <v>VARIASI 3</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Eymar attends classes regularly and completes his lessons on time. He participates actively during sessions and shows interest in learning Roblox development. Eymar follows instructions well and puts in effort to complete his projects. He demonstrates good focus during class and is willing to try new techniques when building his games.</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Araya selalu menyelesaikan lesson tepat waktu bahkan di awal meeting bisa mengerjakan 2 lesson sekaligus . Ia aktif dalam sesi pembelajaran dan terlihat antusias dalam belajar pengembangan Roblox. Araya mampu mengikuti instruksi dengan baik dan berusaha sungguh-sungguh dalam mengerjakan setiap latihan. Ia juga cukup fokus selama kelas berlangsung dan tidak ragu untuk mencoba hal baru saat membuat game-nya. Keep it up Araya!</v>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>NOTES</v>
+        <v>TECH EXPLORER 2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B20" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C20" t="str">
-        <v>VARIASI 3</v>
+        <v>Coding Literacy and Concept</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Design Concept &amp; Practice</v>
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep-konsep coding block pada Scratch, yaitu event, loop, broadcast, looping control (perulangan), dan conditional logic (percabangan). [NAMA_STUDENT] juga mempelajari literasi digital seperti bahaya stranger danger di dunia maya, keamanan digital melalui QR Code, manfaat dan keamanan cloud storage, serta cara kerja search engine. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Awesome [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>NOTES</v>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B25" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C25" t="str">
-        <v>VARIASI 3</v>
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>[NAMA_STUDENT] bisa mengoperasikan Scratch dan menerapkan block coding dengan [sangat baik/ baik/ cukup baik], mulai dari block Motion, Looks, Sound, hingga Sensing. [NAMA_STUDENT] berhasil membuat beberapa project seperti animasi sederhana, Beetle Race Game, dan Bug Hunter Game menggunakan konsep conditional. Nice work [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Character</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ROBLOX EXPLORER 3</v>
+        <v>NOTES</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Coding Literacy and Concept</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B34" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C34" t="str">
-        <v>VARIASI 3</v>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Coding Practice</v>
+        <v>TECH EXPLORER 3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>NOTES</v>
+        <v>Coding Literacy and Concept</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B39" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C39" t="str">
-        <v>VARIASI 3</v>
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep coding lanjutan pada Scratch, yaitu operator, variable, list, dan function (My Blocks), serta konsep otomasi dalam kehidupan sehari-hari. [NAMA_STUDENT] juga mempelajari literasi digital seperti membuat password yang kuat, mengenali deepfake, dasar teknologi Generative AI, teknik prompting yang efektif, dan etika/kejujuran dalam berkarya dengan AI. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Great job [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>[NAMA_STUDENT] bisa menerapkan seluruh konsep yang sudah dipelajari dengan [sangat baik/ baik/ cukup baik] untuk menyelesaikan project game final. [NAMA_STUDENT] mengumpulkan asset game (termasuk dari AI), mengintegrasikan AI Buddy ke dalam VR Edu Delightex, menyelesaikan tahap coding project, hingga mempresentasikan hasil project dengan baik. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A32:C32"/>
-  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A54"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A54"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>GAME DEV 1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Coding Literacy and Concept</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v xml:space="preserve"> Pada level Game Development 1, [NAMA_STUDENT] mempelajari penggunaan framework construct3 untuk membuat 2D game. [NAMA_STUDENT]  menggunakannya dengan [sangat baik/ baik/ cukup baik]. Konsep layout, object, behavior, variable dan event sheet termasuk event dan sub-event juga dipahami dengan cukup baik. Nilai ujian konsep [NAMA_STUDENT]  adalah [MASUKAN_NILAI UJIAN]. Keep it up ya [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>[NAMA_STUDENT]  bisa menambahkan object sprite, background, text, dan behavior seperti Jump-thru, solid, platform, rotate, sine, bullet dan 8Direction. Pada level ini, ada 4 project game. [NAMA_STUDENT]  mengerjakannya dengan [sangat baik/ baik/ cukup baik]. Namun, Saat ujian coding, yaitu membuat sebuah game,  [NAMA_STUDENT]  tidak menyelesaikannya dengan baik. Kedepannya lebih baik lagi dan tingkatkan semangatnya ya [NAMA_STUDENT]!</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>GAME DEV 2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Coding Literacy and Concept</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str" xml:space="preserve">
+        <v xml:space="preserve">
+Progress [NAMA_STUDENT] [sangat signifikan/ signifikan/ cukup signifikan] menggunakan framework construct3 dalam membuat game. Konsep layout game, seperti start, game, gameover dan win layout bisa dipahami [NAMA_STUDENT] dengan [cukup baik/ baik/ sangat baik]. Konsep obstacles, enemies, family features, particles, aim and shoot, change costume and impulse juga bisa dipahami dengan baik. [NAMA_STUDENT] mendapatkan nilai ujian [MASUKAN_NILAI UJIAN]. Pertahankan semangatnya ya [NAMA_STUDENT]!</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>[NAMA_STUDENT] membuat dua game pada level ini. Game yang dibuat semakin kompleks, menggunakan intermediate konsep. [NAMA_STUDENT] berhasil menyelesaikannya dengan [sangat baik/ baik/ cukup baik]. Namun, saat ujian coding, membuat game juga, [NAMA_STUDENT] [cukup/ sedikit] kesulitan untuk menyelesaikannya. Kedepannya lebih banyak latihan codingnya dan tingkatkan semangatnya ya [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>GAME DEV 3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Coding Literacy and Concept</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>[NAMA_STUDENT] semakin mahir menggunakan framework construct3. [NAMA_STUDENT] bisa membuat layout dengan menggunakan konsep tilemap, konsep behaviour scroll to, anchor, dan jump-thru. Konsep-konsep yang dipelajari pada level ini cukup advance dan dapat dipahami dengan [sangat baik/ baik/ cukup baik]. [NAMA_STUDENT] juga bisa men-deploy game yang sudah dibuat ke website. Great Job [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>[NAMA_STUDENT] berhasil menyelesaikan game akhir yang lebih kompleks dari yang sebelumnya pernah dibuat dengan [sangat baik/ baik/ cukup baik]. Untuk project akhir yaitu membuat game sendiri, dimulai dari ide, design, coding sampai presentasi dan demo game, [NAMA_STUDENT] mampu menyelesaikan dengan [sangat baik/ baik/ cukup baik]. Game yang dibuat menarik untuk dimainkan.</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A54"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:A54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>*for report  in english, just translate this</v>
+        <v>ROBLOX EXPLORER 1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>*for character, make it different for each students</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Nilai</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Konversi Kualitas</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Encouragement (ENG)</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Character</v>
+        <v>Coding Literacy and Concept</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ROBLOX DESIGNER 1</v>
-      </c>
-      <c r="G3" t="str">
-        <v>I can tell you’re working hard—stay with it!</v>
-      </c>
-      <c r="H3" t="str">
-        <v>aktif</v>
+        <v>NOTES</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Coding Literacy and Concept</v>
-      </c>
-      <c r="E4" t="str">
-        <v>A</v>
-      </c>
-      <c r="F4" t="str">
-        <v>sangat baik</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Encouragement (IND)</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>NOTES</v>
-      </c>
-      <c r="E5" t="str">
-        <v>B</v>
-      </c>
-      <c r="F5" t="str">
-        <v>baik</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Mantap, Lajutkan ya!</v>
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] perangkat komputer dasar, pengenalan Roblox Studio (menu, shortcut, interface), serta konsep modeling seperti parent &amp; children dan penggunaan terrain editor. [NAMA_STUDENT] juga mempelajari literasi digital seperti pentingnya menghargai copyright/hak cipta karya orang lain. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Well done [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B6" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C6" t="str">
-        <v>VARIASI 3</v>
-      </c>
-      <c r="E6" t="str">
-        <v>C</v>
-      </c>
-      <c r="F6" t="str">
-        <v>cukup baik</v>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Coding Practice</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa mengerjakan latihan design dengan [sangat baik/ baik/ cukup baik] di Roblox Studio, mulai dari membuat model rumah menggunakan referensi Google Image, menambahkan efek dan toolbox, merancang latar belakang map dengan terrain editor (smooth, flatten, brush tool), hingga mem-publish project ke Roblox. Good job [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B11" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C11" t="str">
-        <v>VARIASI 3</v>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] mengikuti kelas dan menyelesaikan tugas tepat waktu. [NAMA_STUDENT] berpartisipasi aktif selama sesi dan menunjukkan minat yang tinggi dalam belajar Roblox development. [NAMA_STUDENT] mengikuti instruksi dengan baik dan berusaha menyelesaikan project-nya. [NAMA_STUDENT] juga menunjukkan fokus yang baik selama kelas dan mau mencoba teknik-teknik baru saat membangun game-nya. Keep it up [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ROBLOX DESIGNER 2</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Coding Literacy and Concept</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>NOTES</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B19" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C19" t="str">
-        <v>VARIASI 3</v>
+        <v>ROBLOX EXPLORER 2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Coding Literacy and Concept</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Coding Practice</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep coding dasar di Roblox Studio, yaitu scripting, properties, variable dan jenisnya, Instance.new(), fungsi wait(), loop, serta while loop. [NAMA_STUDENT] juga mempelajari literasi digital seperti rings of responsibility, screen time, dan cara mengatasi cyberbullying. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Awesome [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B24" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C24" t="str">
-        <v>VARIASI 3</v>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>[NAMA_STUDENT] bisa menerapkan konsep scripting dengan [sangat baik/ baik/ cukup baik]. [NAMA_STUDENT] berhasil membuat game underwater menggunakan solid modeling tool dan memahami gravitasi di Roblox, membuat script untuk part (papan tulisan, suara, atmosphere), serta membuat animasi untuk project Farmland menggunakan while loop untuk menggerakkan object. Nice work [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ROBLOX DESIGNER 3</v>
+        <v>Character</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Coding Literacy and Concept</v>
+        <v>NOTES</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>NOTES</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B33" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C33" t="str">
-        <v>VARIASI 3</v>
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Coding Practice</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>NOTES</v>
+        <v>ROBLOX EXPLORER 3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B38" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C38" t="str">
-        <v>VARIASI 3</v>
+        <v>Coding Literacy and Concept</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep lanjutan di Roblox Studio, yaitu image label, interactive parts, dan penerapan script ke dalam game. [NAMA_STUDENT] juga mempelajari aturan dan etika dalam membuat project. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Great job [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>[NAMA_STUDENT] bisa menerapkan konsep design dan coding dengan [sangat baik/ baik/ cukup baik] untuk project akhir. [NAMA_STUDENT] membuat trap dengan laser beam effect, mengeksplorasi ide dan draft bangunan, melakukan modelling bangunan dengan kombinasi warna dan detail object, menambahkan interactive parts dan scripts, hingga mempresentasikan hasil project Roblox kepada teman-teman sekelas. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A54"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:A54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>*for report  in english, just translate this</v>
+        <v>ROBLOX DESIGNER 1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>*for character, make it different for each students</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Nilai</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Konversi Kualitas</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Encouragement (ENG)</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Character</v>
+        <v>Coding Literacy and Concept</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ROBLOX CODER 1</v>
-      </c>
-      <c r="G3" t="str">
-        <v>I can tell you’re working hard—stay with it!</v>
-      </c>
-      <c r="H3" t="str">
-        <v>aktif</v>
+        <v>NOTES</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Coding Literacy and Concept</v>
-      </c>
-      <c r="E4" t="str">
-        <v>A</v>
-      </c>
-      <c r="F4" t="str">
-        <v>sangat baik</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Encouragement (IND)</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>NOTES</v>
-      </c>
-      <c r="E5" t="str">
-        <v>B</v>
-      </c>
-      <c r="F5" t="str">
-        <v>baik</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Mantap, Lajutkan ya!</v>
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep dasar coding di Roblox Studio, yaitu event, conditional statement, dan cara kerja script untuk objek interaktif seperti kunci, pintu, dan lightswitch. [NAMA_STUDENT] juga mengenal tools desain seperti Photopea untuk membuat asset kostum. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Well done [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B6" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C6" t="str">
-        <v>VARIASI 3</v>
-      </c>
-      <c r="E6" t="str">
-        <v>C</v>
-      </c>
-      <c r="F6" t="str">
-        <v>cukup baik</v>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Coding Practice</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa mengerjakan latihan design dan coding dengan [sangat baik/ baik/ cukup baik]. [NAMA_STUDENT] berhasil membuat map theme park lengkap dengan atmosphere, model interaktif komedi putar, desain baju menggunakan Photopea, storyline dan clue untuk game, modelling kunci dan pintu dengan conditional statement, hingga mem-publish dan memainkan game bersama. Good job [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B11" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C11" t="str">
-        <v>VARIASI 3</v>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ROBLOX CODER 2</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Coding Literacy and Concept</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>NOTES</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B19" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C19" t="str">
-        <v>VARIASI 3</v>
+        <v>ROBLOX DESIGNER 2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Coding Literacy and Concept</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>NOTES</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Coding Practice</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>NOTES</v>
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] penggunaan Blender untuk modeling 3D (basic controls, export/import object ke Roblox Studio), serta konsep screen GUI dan tween service untuk animasi tampilan. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Awesome [NAMA_STUDENT] !</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B24" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C24" t="str">
-        <v>VARIASI 3</v>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>[NAMA_STUDENT] bisa menerapkan konsep modeling dan coding dengan [sangat baik/ baik/ cukup baik]. [NAMA_STUDENT] berhasil membuat model botol dan aksesori player di Blender, mengexport-nya ke Roblox Studio, mendesain screen GUI dengan tween service, membuat model low poly untuk object utama Finding Game, hingga membuat coding untuk mengambil objek yang ditemukan. Nice work [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ROBLOX CODER 3</v>
+        <v>Character</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Coding Literacy and Concept</v>
+        <v>NOTES</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>NOTES</v>
+        <v>VARIASI 1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B33" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C33" t="str">
-        <v>VARIASI 3</v>
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Coding Practice</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>NOTES</v>
+        <v>ROBLOX DESIGNER 3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>VARIASI 1</v>
-      </c>
-      <c r="B38" t="str">
-        <v>VARIASI 2</v>
-      </c>
-      <c r="C38" t="str">
-        <v>VARIASI 3</v>
+        <v>Coding Literacy and Concept</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>[NAMA_STUDENT] bisa memahami dengan [sangat baik/ baik/ cukup baik] konsep lanjutan Roblox Studio, yaitu places dan fungsinya, struktur thumbnail dan game icon, serta script teleport dengan event touch. Saat ujian konsep, [NAMA_STUDENT] mendapatkan score [MASUKAN_NILAI UJIAN]. Great job [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Coding Practice</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>[NAMA_STUDENT] bisa menerapkan konsep design dan coding dengan [sangat baik/ baik/ cukup baik] untuk project akhir. [NAMA_STUDENT] menggabungkan beberapa game ke dalam satu lobby, membuat badges, game pass, dan opening GUI, menambahkan tween animation dan kode misi dengan script teleport, hingga mempresentasikan project game yang sudah selesai kepada teman-teman sekelas. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Character</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>VARIASI 1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>[NAMA_STUDENT] [sangat aktif/ aktif/ cukup aktif] di kelas dan berinteraksi baik dengan teacher dan teman-temannya di kelas. Ia juga  [sangat aktif/ aktif/ cukup aktif] bertanya tentang materi yang kurang dipahami. [NAMA_STUDENT] juga fokus/cukup fokus ketika belajar walaupun kadang-kadang suasana kelas kurang kondusif. Keep it up [NAMA_STUDENT] !</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A54"/>
   </ignoredErrors>
 </worksheet>
 </file>